--- a/translation/review/000scriptAKYO_0034A.xlsx
+++ b/translation/review/000scriptAKYO_0034A.xlsx
@@ -55,7 +55,7 @@
     <t>History is built upon a large quantity of dead bodies.</t>
   </si>
   <si>
-    <t>La historia se construye sobre una gran cantidad de cadáveres.</t>
+    <t>La historia se construye sobre una gran cantidad＿de cadáveres.</t>
   </si>
   <si>
     <t>I don't understand that at all!</t>
@@ -67,7 +67,7 @@
     <t>Well, to put it simply, you're just adding to the numbers.</t>
   </si>
   <si>
-    <t>Bueno, en pocas palabras, solo estás aumentando los números.</t>
+    <t>Bueno, en pocas palabras, solo estás＿aumentando los números.</t>
   </si>
 </sst>
 </file>
